--- a/tiflow-diga/main/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
+++ b/tiflow-diga/main/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3809" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3809" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -634,7 +634,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
+    <t>Extension</t>
   </si>
   <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
@@ -740,9 +740,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_RedeemCode}
 </t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -4398,7 +4395,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -5147,10 +5144,10 @@
         <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5233,13 +5230,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
@@ -5261,13 +5258,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5350,10 +5347,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5379,16 +5376,16 @@
         <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5437,7 +5434,7 @@
         <v>116</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5469,10 +5466,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5495,16 +5492,16 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5542,7 +5539,7 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5552,7 +5549,7 @@
         <v>116</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5567,30 +5564,30 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>79</v>
@@ -5612,16 +5609,16 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="N29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5632,7 +5629,7 @@
         <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>79</v>
@@ -5671,7 +5668,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5686,30 +5683,30 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>79</v>
@@ -5731,16 +5728,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="M30" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5751,7 +5748,7 @@
         <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>79</v>
@@ -5790,7 +5787,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5805,27 +5802,27 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5848,16 +5845,16 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5907,7 +5904,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5919,13 +5916,13 @@
         <v>151</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5939,10 +5936,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5968,13 +5965,13 @@
         <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5982,7 +5979,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>79</v>
@@ -6000,14 +5997,14 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
       </c>
@@ -6024,7 +6021,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>89</v>
@@ -6039,16 +6036,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6056,10 +6053,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6082,13 +6079,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6118,11 +6115,11 @@
         <v>158</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
       </c>
@@ -6139,7 +6136,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6154,10 +6151,10 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6171,10 +6168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6197,16 +6194,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6232,14 +6229,14 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
       </c>
@@ -6256,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6274,24 +6271,24 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6314,16 +6311,16 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6373,7 +6370,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6388,27 +6385,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6520,10 +6517,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6637,13 +6634,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6665,13 +6662,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6740,7 +6737,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -6754,10 +6751,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6869,10 +6866,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6986,10 +6983,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7029,7 +7026,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>79</v>
@@ -7103,10 +7100,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7132,10 +7129,10 @@
         <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7147,7 +7144,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7162,11 +7159,11 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -7216,10 +7213,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7245,13 +7242,13 @@
         <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7301,16 +7298,16 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
@@ -7333,10 +7330,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7362,13 +7359,13 @@
         <v>131</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7397,28 +7394,28 @@
         <v>147</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z44" t="s" s="2">
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7450,10 +7447,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7476,16 +7473,16 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7535,7 +7532,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7553,7 +7550,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7562,15 +7559,15 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7682,10 +7679,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7799,10 +7796,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7828,16 +7825,16 @@
         <v>168</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7862,31 +7859,31 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7904,7 +7901,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7918,10 +7915,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7944,19 +7941,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7984,28 +7981,28 @@
         <v>147</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8023,7 +8020,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -8032,15 +8029,15 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8066,65 +8063,65 @@
         <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T50" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="S50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T50" t="s" s="2">
+      <c r="U50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8142,24 +8139,24 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>380</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8185,13 +8182,13 @@
         <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8205,43 +8202,43 @@
         <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8259,24 +8256,24 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8299,16 +8296,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8358,7 +8355,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8370,30 +8367,30 @@
         <v>151</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8416,16 +8413,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8475,7 +8472,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8487,30 +8484,30 @@
         <v>151</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8536,13 +8533,13 @@
         <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8592,7 +8589,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8624,10 +8621,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8650,16 +8647,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8709,7 +8706,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8721,30 +8718,30 @@
         <v>151</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8856,10 +8853,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8973,10 +8970,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9002,13 +8999,13 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9058,16 +9055,16 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -9090,10 +9087,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9119,13 +9116,13 @@
         <v>131</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9154,10 +9151,10 @@
         <v>147</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9175,7 +9172,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9207,10 +9204,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9233,16 +9230,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9292,7 +9289,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9310,7 +9307,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9319,15 +9316,15 @@
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9353,13 +9350,13 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9409,7 +9406,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9441,10 +9438,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9467,16 +9464,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9526,7 +9523,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9538,13 +9535,13 @@
         <v>151</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9558,10 +9555,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9584,16 +9581,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9643,7 +9640,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9655,16 +9652,16 @@
         <v>151</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9675,10 +9672,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9701,13 +9698,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9758,7 +9755,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9773,10 +9770,10 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9790,10 +9787,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9905,10 +9902,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10022,14 +10019,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10051,16 +10048,16 @@
         <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10109,7 +10106,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10141,10 +10138,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10167,19 +10164,19 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10207,11 +10204,11 @@
         <v>158</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10228,7 +10225,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10246,7 +10243,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10255,15 +10252,15 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10286,16 +10283,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10345,7 +10342,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -10357,13 +10354,13 @@
         <v>151</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -10377,10 +10374,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10492,10 +10489,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10609,10 +10606,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10638,13 +10635,13 @@
         <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10694,16 +10691,16 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI72" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
@@ -10726,10 +10723,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10755,13 +10752,13 @@
         <v>131</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10790,28 +10787,28 @@
         <v>147</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z73" t="s" s="2">
+      <c r="AA73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10843,10 +10840,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10869,16 +10866,16 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="M74" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10928,7 +10925,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10946,7 +10943,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -10955,15 +10952,15 @@
         <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10989,13 +10986,13 @@
         <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11045,7 +11042,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11077,10 +11074,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11103,16 +11100,16 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11162,7 +11159,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11174,13 +11171,13 @@
         <v>151</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
@@ -11194,10 +11191,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11220,16 +11217,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11279,7 +11276,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11291,30 +11288,30 @@
         <v>151</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11426,10 +11423,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11543,10 +11540,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11572,13 +11569,13 @@
         <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11628,16 +11625,16 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI80" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>101</v>
@@ -11660,10 +11657,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11689,13 +11686,13 @@
         <v>131</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11724,10 +11721,10 @@
         <v>147</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11745,7 +11742,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11777,10 +11774,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11803,16 +11800,16 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11862,7 +11859,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11880,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
@@ -11889,15 +11886,15 @@
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11923,13 +11920,13 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11979,7 +11976,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12011,10 +12008,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12037,16 +12034,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="N84" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12075,11 +12072,11 @@
         <v>158</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12096,7 +12093,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12114,24 +12111,24 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12154,16 +12151,16 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12213,7 +12210,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12225,30 +12222,30 @@
         <v>151</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AM85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12271,16 +12268,16 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="N86" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12330,7 +12327,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12342,30 +12339,30 @@
         <v>151</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>516</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12388,13 +12385,13 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12445,7 +12442,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12463,24 +12460,24 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AM87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12503,13 +12500,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12560,7 +12557,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12572,30 +12569,30 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AK88" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AK88" t="s" s="2">
+      <c r="AL88" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AL88" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AM88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12618,16 +12615,16 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N89" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12677,7 +12674,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12689,30 +12686,30 @@
         <v>151</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12735,16 +12732,16 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>539</v>
-      </c>
       <c r="N90" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12794,7 +12791,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12806,19 +12803,19 @@
         <v>151</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -12826,10 +12823,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12852,16 +12849,16 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12911,7 +12908,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12926,27 +12923,27 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AL91" t="s" s="2">
+      <c r="AM91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12969,16 +12966,16 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13028,7 +13025,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13037,16 +13034,16 @@
         <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL92" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
@@ -13060,10 +13057,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13086,16 +13083,16 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13145,7 +13142,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13163,13 +13160,13 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13177,10 +13174,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13292,10 +13289,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13409,14 +13406,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13438,16 +13435,16 @@
         <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -13496,7 +13493,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13528,10 +13525,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13554,13 +13551,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13611,7 +13608,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>89</v>
@@ -13629,7 +13626,7 @@
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>79</v>
@@ -13643,10 +13640,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13669,16 +13666,16 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="N98" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13707,11 +13704,11 @@
         <v>158</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13728,7 +13725,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13746,24 +13743,24 @@
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13786,16 +13783,16 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13824,11 +13821,11 @@
         <v>158</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z99" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z99" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
       </c>
@@ -13845,7 +13842,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13863,24 +13860,24 @@
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AM99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="AO99" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13903,16 +13900,16 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13962,7 +13959,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -13974,19 +13971,19 @@
         <v>151</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -13994,14 +13991,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14020,16 +14017,16 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14079,7 +14076,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14091,13 +14088,13 @@
         <v>151</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>79</v>
@@ -14111,10 +14108,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14137,16 +14134,16 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14196,7 +14193,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14208,13 +14205,13 @@
         <v>151</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>79</v>
